--- a/ig/test-tabs-svs/ValueSet-vs-tre-r361-fonction-publique-all.xlsx
+++ b/ig/test-tabs-svs/ValueSet-vs-tre-r361-fonction-publique-all.xlsx
@@ -8,12 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion Parameters" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
   <si>
     <t>Property</t>
   </si>
@@ -106,6 +108,57 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r361-fonction-publique</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r361-fonction-publique|20260330120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>Fonction Publique d'état</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Fonction Publique Hospitalière</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Fonction publique Territoriale</t>
   </si>
 </sst>
 </file>
@@ -397,4 +450,134 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>